--- a/LP_Error_Log.xlsx
+++ b/LP_Error_Log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29926"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://musigma-my.sharepoint.com/personal/rajkumar_r_mu-sigma_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://musigma-my.sharepoint.com/personal/maria_daniels_mu-sigma_com/Documents/Documents/exel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="8_{5EB6F39B-016E-4168-A8C8-22C4E1775C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{215647DE-0F92-44F2-BCA3-2714F1CEECC5}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="8_{5EB6F39B-016E-4168-A8C8-22C4E1775C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3AF0C60-40EE-4174-981C-2973AC526073}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{7E36AAAB-D706-4463-8B8E-FC781FC93857}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{7E36AAAB-D706-4463-8B8E-FC781FC93857}"/>
   </bookViews>
   <sheets>
     <sheet name="Error Log" sheetId="1" r:id="rId1"/>
@@ -797,9 +797,6 @@
     <t>Venkata B</t>
   </si>
   <si>
-    <t>Test</t>
-  </si>
-  <si>
     <t>Error</t>
   </si>
   <si>
@@ -819,13 +816,16 @@
   </si>
   <si>
     <t>Adhoc</t>
+  </si>
+  <si>
+    <t>Testing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1624,30 +1624,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDFA68B3-D723-4F82-915D-45274FA59027}">
   <dimension ref="A2:Q27"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.5703125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="61.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.54296875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.453125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="61.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="170.7109375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="170.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="53.140625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.7109375" style="2"/>
-    <col min="18" max="34" width="8.7109375" style="1"/>
-    <col min="35" max="37" width="9.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="8.7109375" style="1"/>
+    <col min="11" max="11" width="9.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="170.7265625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="170.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="53.1796875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.1796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.7265625" style="2"/>
+    <col min="18" max="34" width="8.7265625" style="1"/>
+    <col min="35" max="37" width="9.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" customFormat="1" ht="28.5">
+    <row r="2" spans="2:16" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="2:16" ht="42.75">
+    <row r="3" spans="2:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B3" s="10">
         <v>45846</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="2:16" ht="28.5">
+    <row r="4" spans="2:16" ht="29" x14ac:dyDescent="0.35">
       <c r="B4" s="15">
         <v>45875</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="2:16" ht="28.5">
+    <row r="5" spans="2:16" ht="29" x14ac:dyDescent="0.35">
       <c r="B5" s="15">
         <v>45896</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="2:16">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B6" s="10" t="s">
         <v>43</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="71.25">
+    <row r="7" spans="2:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="B7" s="10" t="s">
         <v>51</v>
       </c>
@@ -1927,7 +1927,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="2:16" s="5" customFormat="1">
+    <row r="8" spans="2:16" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B8" s="15">
         <v>45890</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="2:16" ht="28.5">
+    <row r="9" spans="2:16" ht="29" x14ac:dyDescent="0.35">
       <c r="B9" s="18">
         <v>45873</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="2:16" s="6" customFormat="1" ht="28.5">
+    <row r="10" spans="2:16" s="6" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="B10" s="22">
         <v>45889</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="2:16">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B11" s="22">
         <v>45876</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:16">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B12" s="23">
         <v>45833</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="2:16" ht="42.75">
+    <row r="13" spans="2:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B13" s="7">
         <v>45896</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="2:16">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B14" s="7">
         <v>45929</v>
       </c>
@@ -2248,7 +2248,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="2:16" ht="28.5">
+    <row r="15" spans="2:16" ht="29" x14ac:dyDescent="0.35">
       <c r="B15" s="7">
         <v>45849</v>
       </c>
@@ -2295,7 +2295,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="2:16" ht="76.5" customHeight="1">
+    <row r="16" spans="2:16" ht="76.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="7">
         <v>45929</v>
       </c>
@@ -2342,7 +2342,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="2:16" ht="39.75">
+    <row r="17" spans="2:16" ht="39.5" x14ac:dyDescent="0.35">
       <c r="B17" s="7">
         <v>45966</v>
       </c>
@@ -2389,7 +2389,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="2:16" ht="42.75">
+    <row r="18" spans="2:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B18" s="7">
         <v>45938</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="2:16" ht="85.5">
+    <row r="19" spans="2:16" ht="87" x14ac:dyDescent="0.35">
       <c r="B19" s="36">
         <v>45942</v>
       </c>
@@ -2479,7 +2479,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="2:16">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B20" s="40">
         <v>45788</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="2:16" ht="28.5">
+    <row r="21" spans="2:16" ht="29" x14ac:dyDescent="0.35">
       <c r="B21" s="40">
         <v>45966</v>
       </c>
@@ -2570,7 +2570,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="2:16">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B22" s="40">
         <v>45978</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="2:16" ht="85.5">
+    <row r="23" spans="2:16" ht="87" x14ac:dyDescent="0.35">
       <c r="B23" s="40"/>
       <c r="C23" s="43"/>
       <c r="E23" s="1" t="s">
@@ -2657,7 +2657,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="24" spans="2:16" ht="71.25">
+    <row r="24" spans="2:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="B24" s="44" t="s">
         <v>157</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="25" spans="2:16">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B25" s="49">
         <v>46034</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="26" spans="2:16">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B26" s="7">
         <v>46044</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="2:16" ht="99.75">
+    <row r="27" spans="2:16" ht="101.5" x14ac:dyDescent="0.35">
       <c r="B27" s="7">
         <v>46072</v>
       </c>
@@ -2900,13 +2900,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8153D2D9-0413-442D-91E8-9BA8C9668BAB}">
   <dimension ref="A1:B41"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="56" t="s">
         <v>186</v>
       </c>
@@ -2914,7 +2914,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>188</v>
       </c>
@@ -2922,7 +2922,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>189</v>
       </c>
@@ -2930,7 +2930,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>190</v>
       </c>
@@ -2938,7 +2938,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>191</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>192</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>193</v>
       </c>
@@ -2962,7 +2962,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>194</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>195</v>
       </c>
@@ -2978,7 +2978,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>197</v>
       </c>
@@ -2986,7 +2986,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>198</v>
       </c>
@@ -2994,7 +2994,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>200</v>
       </c>
@@ -3002,7 +3002,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>201</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>202</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>203</v>
       </c>
@@ -3026,7 +3026,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>204</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>205</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>206</v>
       </c>
@@ -3050,7 +3050,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>207</v>
       </c>
@@ -3058,7 +3058,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>208</v>
       </c>
@@ -3066,7 +3066,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>209</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>210</v>
       </c>
@@ -3082,7 +3082,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>212</v>
       </c>
@@ -3090,7 +3090,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>214</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>216</v>
       </c>
@@ -3106,7 +3106,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>218</v>
       </c>
@@ -3114,7 +3114,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>220</v>
       </c>
@@ -3122,7 +3122,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>222</v>
       </c>
@@ -3130,7 +3130,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="57" t="s">
         <v>224</v>
       </c>
@@ -3138,7 +3138,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="57" t="s">
         <v>226</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="57" t="s">
         <v>227</v>
       </c>
@@ -3154,7 +3154,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="57" t="s">
         <v>228</v>
       </c>
@@ -3162,7 +3162,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="57" t="s">
         <v>229</v>
       </c>
@@ -3170,7 +3170,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="57" t="s">
         <v>230</v>
       </c>
@@ -3178,7 +3178,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="57" t="s">
         <v>232</v>
       </c>
@@ -3186,7 +3186,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="57" t="s">
         <v>233</v>
       </c>
@@ -3194,7 +3194,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="57" t="s">
         <v>234</v>
       </c>
@@ -3202,7 +3202,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="57" t="s">
         <v>235</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="57" t="s">
         <v>236</v>
       </c>
@@ -3218,7 +3218,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="57" t="s">
         <v>237</v>
       </c>
@@ -3226,9 +3226,9 @@
         <v>130</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="B41" t="s">
         <v>125</v>
@@ -3243,23 +3243,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE0945BE-3BA7-425F-BF75-6E828DF826F2}">
   <dimension ref="A2:E12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -3287,13 +3287,13 @@
         <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E4" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -3301,40 +3301,40 @@
         <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D8" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D9" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D10" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="D10" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D11" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="D11" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D12" t="s">
         <v>17</v>
       </c>
@@ -3345,6 +3345,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="2260421e-e696-4c36-bc86-ab4f4887566a" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="50c8ec5c-00a3-44d9-9629-927e8823181b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003817D065C249F1458CB8354A869F4BA5" ma:contentTypeVersion="21" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b70cb07eff86d14135a5b65da9aa9ead">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="2260421e-e696-4c36-bc86-ab4f4887566a" xmlns:ns3="50c8ec5c-00a3-44d9-9629-927e8823181b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c70ade665b74142d9371c6619ef8a893" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -3622,36 +3644,42 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="2260421e-e696-4c36-bc86-ab4f4887566a" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="50c8ec5c-00a3-44d9-9629-927e8823181b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3B298BF-25E8-46BA-9DE8-DCF1171FFF91}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AD69449-6A98-4E73-8650-98380FFF9950}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2260421e-e696-4c36-bc86-ab4f4887566a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="50c8ec5c-00a3-44d9-9629-927e8823181b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AB6057F-A959-4F8E-984C-EB28D0896B30}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AB6057F-A959-4F8E-984C-EB28D0896B30}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AD69449-6A98-4E73-8650-98380FFF9950}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3B298BF-25E8-46BA-9DE8-DCF1171FFF91}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="2260421e-e696-4c36-bc86-ab4f4887566a"/>
+    <ds:schemaRef ds:uri="50c8ec5c-00a3-44d9-9629-927e8823181b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/LP_Error_Log.xlsx
+++ b/LP_Error_Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://musigma-my.sharepoint.com/personal/maria_daniels_mu-sigma_com/Documents/Documents/exel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="8_{5EB6F39B-016E-4168-A8C8-22C4E1775C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3AF0C60-40EE-4174-981C-2973AC526073}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="8_{5EB6F39B-016E-4168-A8C8-22C4E1775C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDBA8A55-5B98-479E-9C20-2E92142B00C7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{7E36AAAB-D706-4463-8B8E-FC781FC93857}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7E36AAAB-D706-4463-8B8E-FC781FC93857}"/>
   </bookViews>
   <sheets>
     <sheet name="Error Log" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Sheet2" sheetId="2" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Error Log'!$B$2:$P$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Error Log'!$B$2:$P$27</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="246">
   <si>
     <t>Rollout Date</t>
   </si>
@@ -818,7 +818,7 @@
     <t>Adhoc</t>
   </si>
   <si>
-    <t>Testing</t>
+    <t>SAHANA</t>
   </si>
 </sst>
 </file>
@@ -1623,6 +1623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDFA68B3-D723-4F82-915D-45274FA59027}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A2:Q27"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1694,7 +1695,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="2:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:16" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B3" s="10">
         <v>45846</v>
       </c>
@@ -1741,7 +1742,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="2:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:16" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="B4" s="15">
         <v>45875</v>
       </c>
@@ -1788,7 +1789,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="2:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:16" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="B5" s="15">
         <v>45896</v>
       </c>
@@ -1835,7 +1836,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B6" s="10" t="s">
         <v>43</v>
       </c>
@@ -1882,7 +1883,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:16" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B7" s="10" t="s">
         <v>51</v>
       </c>
@@ -1950,7 +1951,7 @@
         <v>38</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>62</v>
+        <v>245</v>
       </c>
       <c r="J8" s="10">
         <v>2</v>
@@ -1997,7 +1998,7 @@
         <v>69</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>62</v>
+        <v>245</v>
       </c>
       <c r="J9" s="10">
         <v>2</v>
@@ -2044,7 +2045,7 @@
         <v>77</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>62</v>
+        <v>245</v>
       </c>
       <c r="J10" s="10">
         <v>2</v>
@@ -2068,7 +2069,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B11" s="22">
         <v>45876</v>
       </c>
@@ -2115,7 +2116,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B12" s="23">
         <v>45833</v>
       </c>
@@ -2160,7 +2161,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="2:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:16" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B13" s="7">
         <v>45896</v>
       </c>
@@ -2207,7 +2208,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B14" s="7">
         <v>45929</v>
       </c>
@@ -2248,7 +2249,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="2:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:16" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="B15" s="7">
         <v>45849</v>
       </c>
@@ -2295,7 +2296,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="2:16" ht="76.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:16" ht="76.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="7">
         <v>45929</v>
       </c>
@@ -2342,7 +2343,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="2:16" ht="39.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:16" ht="39.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B17" s="7">
         <v>45966</v>
       </c>
@@ -2389,7 +2390,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="2:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:16" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B18" s="7">
         <v>45938</v>
       </c>
@@ -2434,7 +2435,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="2:16" ht="87" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:16" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="B19" s="36">
         <v>45942</v>
       </c>
@@ -2479,7 +2480,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B20" s="40">
         <v>45788</v>
       </c>
@@ -2526,7 +2527,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="2:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:16" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="B21" s="40">
         <v>45966</v>
       </c>
@@ -2570,7 +2571,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B22" s="40">
         <v>45978</v>
       </c>
@@ -2617,7 +2618,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="2:16" ht="87" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:16" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="B23" s="40"/>
       <c r="C23" s="43"/>
       <c r="E23" s="1" t="s">
@@ -2657,7 +2658,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="24" spans="2:16" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:16" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B24" s="44" t="s">
         <v>157</v>
       </c>
@@ -2704,7 +2705,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B25" s="49">
         <v>46034</v>
       </c>
@@ -2751,7 +2752,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B26" s="7">
         <v>46044</v>
       </c>
@@ -2799,7 +2800,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="2:16" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:16" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B27" s="7">
         <v>46072</v>
       </c>
@@ -2847,7 +2848,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:P26" xr:uid="{DDFA68B3-D723-4F82-915D-45274FA59027}"/>
+  <autoFilter ref="B2:P27" xr:uid="{DDFA68B3-D723-4F82-915D-45274FA59027}">
+    <filterColumn colId="7">
+      <filters>
+        <filter val="SA"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="B19">
     <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
@@ -2899,7 +2906,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8153D2D9-0413-442D-91E8-9BA8C9668BAB}">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.453125" bestFit="1" customWidth="1"/>
@@ -3224,14 +3231,6 @@
       </c>
       <c r="B40" s="57" t="s">
         <v>130</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>245</v>
-      </c>
-      <c r="B41" t="s">
-        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -3345,28 +3344,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="2260421e-e696-4c36-bc86-ab4f4887566a" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="50c8ec5c-00a3-44d9-9629-927e8823181b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003817D065C249F1458CB8354A869F4BA5" ma:contentTypeVersion="21" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b70cb07eff86d14135a5b65da9aa9ead">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="2260421e-e696-4c36-bc86-ab4f4887566a" xmlns:ns3="50c8ec5c-00a3-44d9-9629-927e8823181b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c70ade665b74142d9371c6619ef8a893" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -3644,27 +3621,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AD69449-6A98-4E73-8650-98380FFF9950}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2260421e-e696-4c36-bc86-ab4f4887566a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="50c8ec5c-00a3-44d9-9629-927e8823181b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AB6057F-A959-4F8E-984C-EB28D0896B30}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="2260421e-e696-4c36-bc86-ab4f4887566a" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="50c8ec5c-00a3-44d9-9629-927e8823181b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3B298BF-25E8-46BA-9DE8-DCF1171FFF91}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3682,4 +3661,24 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AB6057F-A959-4F8E-984C-EB28D0896B30}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AD69449-6A98-4E73-8650-98380FFF9950}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2260421e-e696-4c36-bc86-ab4f4887566a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="50c8ec5c-00a3-44d9-9629-927e8823181b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/LP_Error_Log.xlsx
+++ b/LP_Error_Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://musigma-my.sharepoint.com/personal/maria_daniels_mu-sigma_com/Documents/Documents/exel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="8_{5EB6F39B-016E-4168-A8C8-22C4E1775C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDBA8A55-5B98-479E-9C20-2E92142B00C7}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="8_{5EB6F39B-016E-4168-A8C8-22C4E1775C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD65717F-C4D8-4C8A-A452-759C7E7DB61F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7E36AAAB-D706-4463-8B8E-FC781FC93857}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{7E36AAAB-D706-4463-8B8E-FC781FC93857}"/>
   </bookViews>
   <sheets>
     <sheet name="Error Log" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="245">
   <si>
     <t>Rollout Date</t>
   </si>
@@ -274,9 +274,6 @@
   </si>
   <si>
     <t>SUPP0000362 - UBK</t>
-  </si>
-  <si>
-    <t>SAM</t>
   </si>
   <si>
     <t>MG</t>
@@ -1928,7 +1925,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="2:16" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:16" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="B8" s="15">
         <v>45890</v>
       </c>
@@ -1951,7 +1948,7 @@
         <v>38</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J8" s="10">
         <v>2</v>
@@ -1975,7 +1972,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="2:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:16" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="B9" s="18">
         <v>45873</v>
       </c>
@@ -1998,7 +1995,7 @@
         <v>69</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J9" s="10">
         <v>2</v>
@@ -2039,13 +2036,13 @@
         <v>29</v>
       </c>
       <c r="G10" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="H10" s="10" t="s">
-        <v>77</v>
-      </c>
       <c r="I10" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J10" s="10">
         <v>2</v>
@@ -2057,13 +2054,13 @@
         <v>22</v>
       </c>
       <c r="M10" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="N10" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="N10" s="12" t="s">
+      <c r="O10" s="12" t="s">
         <v>79</v>
-      </c>
-      <c r="O10" s="12" t="s">
-        <v>80</v>
       </c>
       <c r="P10" s="14" t="s">
         <v>26</v>
@@ -2077,10 +2074,10 @@
         <v>8603171767</v>
       </c>
       <c r="D11" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" s="11" t="s">
         <v>81</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>82</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>29</v>
@@ -2104,10 +2101,10 @@
         <v>22</v>
       </c>
       <c r="M11" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="N11" s="14" t="s">
         <v>83</v>
-      </c>
-      <c r="N11" s="14" t="s">
-        <v>84</v>
       </c>
       <c r="O11" s="14" t="s">
         <v>65</v>
@@ -2122,13 +2119,13 @@
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="F12" s="10" t="s">
         <v>86</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>87</v>
       </c>
       <c r="G12" s="10" t="s">
         <v>61</v>
@@ -2149,13 +2146,13 @@
         <v>22</v>
       </c>
       <c r="M12" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="N12" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="N12" s="14" t="s">
+      <c r="O12" s="14" t="s">
         <v>89</v>
-      </c>
-      <c r="O12" s="14" t="s">
-        <v>90</v>
       </c>
       <c r="P12" s="14" t="s">
         <v>26</v>
@@ -2169,22 +2166,22 @@
         <v>9710698750</v>
       </c>
       <c r="D13" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="E13" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="E13" s="26" t="s">
+      <c r="F13" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="F13" s="24" t="s">
+      <c r="G13" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="H13" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="H13" s="25" t="s">
+      <c r="I13" s="25" t="s">
         <v>95</v>
-      </c>
-      <c r="I13" s="25" t="s">
-        <v>96</v>
       </c>
       <c r="J13" s="25">
         <v>3</v>
@@ -2196,13 +2193,13 @@
         <v>70</v>
       </c>
       <c r="M13" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="N13" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="N13" s="27" t="s">
+      <c r="O13" s="27" t="s">
         <v>98</v>
-      </c>
-      <c r="O13" s="27" t="s">
-        <v>99</v>
       </c>
       <c r="P13" s="25" t="s">
         <v>26</v>
@@ -2216,16 +2213,16 @@
         <v>9255687608</v>
       </c>
       <c r="D14" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="E14" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="F14" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="F14" s="24" t="s">
-        <v>102</v>
-      </c>
       <c r="G14" s="25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H14" s="25" t="s">
         <v>38</v>
@@ -2254,25 +2251,25 @@
         <v>45849</v>
       </c>
       <c r="C15" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="D15" s="29" t="s">
+      <c r="E15" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="F15" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="F15" s="25" t="s">
-        <v>106</v>
-      </c>
       <c r="G15" s="25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H15" s="25" t="s">
         <v>19</v>
       </c>
       <c r="I15" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J15" s="25">
         <v>3</v>
@@ -2284,13 +2281,13 @@
         <v>22</v>
       </c>
       <c r="M15" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="N15" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="N15" s="31" t="s">
+      <c r="O15" s="31" t="s">
         <v>108</v>
-      </c>
-      <c r="O15" s="31" t="s">
-        <v>109</v>
       </c>
       <c r="P15" s="25" t="s">
         <v>26</v>
@@ -2304,16 +2301,16 @@
         <v>8603239765</v>
       </c>
       <c r="D16" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="E16" s="26" t="s">
+      <c r="F16" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="G16" s="25" t="s">
         <v>111</v>
-      </c>
-      <c r="F16" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="G16" s="25" t="s">
-        <v>112</v>
       </c>
       <c r="H16" s="25" t="s">
         <v>68</v>
@@ -2331,13 +2328,13 @@
         <v>70</v>
       </c>
       <c r="M16" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="N16" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="N16" s="27" t="s">
+      <c r="O16" s="27" t="s">
         <v>114</v>
-      </c>
-      <c r="O16" s="27" t="s">
-        <v>115</v>
       </c>
       <c r="P16" s="25" t="s">
         <v>26</v>
@@ -2351,22 +2348,22 @@
         <v>8631504486</v>
       </c>
       <c r="D17" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="E17" s="33" t="s">
         <v>116</v>
       </c>
-      <c r="E17" s="33" t="s">
+      <c r="F17" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="H17" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="F17" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="G17" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="H17" s="25" t="s">
+      <c r="I17" s="25" t="s">
         <v>118</v>
-      </c>
-      <c r="I17" s="25" t="s">
-        <v>119</v>
       </c>
       <c r="J17" s="25">
         <v>3</v>
@@ -2378,13 +2375,13 @@
         <v>22</v>
       </c>
       <c r="M17" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="N17" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="N17" s="27" t="s">
+      <c r="O17" s="38" t="s">
         <v>121</v>
-      </c>
-      <c r="O17" s="38" t="s">
-        <v>122</v>
       </c>
       <c r="P17" s="25" t="s">
         <v>26</v>
@@ -2398,22 +2395,22 @@
         <v>8622526246</v>
       </c>
       <c r="D18" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="E18" s="39" t="s">
         <v>123</v>
-      </c>
-      <c r="E18" s="39" t="s">
-        <v>124</v>
       </c>
       <c r="F18" s="25" t="s">
         <v>17</v>
       </c>
       <c r="G18" s="25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H18" s="25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I18" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J18" s="25">
         <v>3</v>
@@ -2425,10 +2422,10 @@
         <v>70</v>
       </c>
       <c r="M18" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="N18" s="27" t="s">
         <v>126</v>
-      </c>
-      <c r="N18" s="27" t="s">
-        <v>127</v>
       </c>
       <c r="O18" s="25"/>
       <c r="P18" s="25" t="s">
@@ -2443,10 +2440,10 @@
         <v>8603316297</v>
       </c>
       <c r="D19" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="E19" s="33" t="s">
         <v>128</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>129</v>
       </c>
       <c r="F19" s="25" t="s">
         <v>17</v>
@@ -2455,10 +2452,10 @@
         <v>18</v>
       </c>
       <c r="H19" s="37" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I19" s="37" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J19" s="25">
         <v>3</v>
@@ -2470,10 +2467,10 @@
         <v>70</v>
       </c>
       <c r="M19" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="N19" s="27" t="s">
         <v>131</v>
-      </c>
-      <c r="N19" s="27" t="s">
-        <v>132</v>
       </c>
       <c r="O19" s="25"/>
       <c r="P19" s="25" t="s">
@@ -2488,19 +2485,19 @@
         <v>8622526203</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="G20" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="H20" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>39</v>
@@ -2515,13 +2512,13 @@
         <v>70</v>
       </c>
       <c r="M20" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="N20" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="N20" s="1" t="s">
+      <c r="O20" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="P20" s="25" t="s">
         <v>26</v>
@@ -2535,16 +2532,16 @@
         <v>8631786258</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>38</v>
@@ -2562,10 +2559,10 @@
         <v>70</v>
       </c>
       <c r="M21" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="N21" s="41" t="s">
         <v>144</v>
-      </c>
-      <c r="N21" s="41" t="s">
-        <v>145</v>
       </c>
       <c r="P21" s="25" t="s">
         <v>26</v>
@@ -2579,19 +2576,19 @@
         <v>8631706519</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="F22" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="H22" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>39</v>
@@ -2606,13 +2603,13 @@
         <v>70</v>
       </c>
       <c r="M22" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="N22" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="N22" s="1" t="s">
+      <c r="O22" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="P22" s="25" t="s">
         <v>26</v>
@@ -2622,13 +2619,13 @@
       <c r="B23" s="40"/>
       <c r="C23" s="43"/>
       <c r="E23" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>19</v>
@@ -2646,42 +2643,42 @@
         <v>70</v>
       </c>
       <c r="M23" s="41" t="s">
+        <v>152</v>
+      </c>
+      <c r="N23" s="41" t="s">
         <v>153</v>
       </c>
-      <c r="N23" s="41" t="s">
+      <c r="O23" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="O23" s="41" t="s">
+      <c r="P23" s="25" t="s">
         <v>155</v>
-      </c>
-      <c r="P23" s="25" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="24" spans="2:16" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="B24" s="44" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C24" s="45">
         <v>10583596622</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="F24" t="s">
         <v>159</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="G24" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="H24" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J24" s="1">
         <v>3</v>
@@ -2693,16 +2690,16 @@
         <v>70</v>
       </c>
       <c r="M24" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="N24" s="41" t="s">
         <v>162</v>
       </c>
-      <c r="N24" s="41" t="s">
+      <c r="O24" s="41" t="s">
         <v>163</v>
       </c>
-      <c r="O24" s="41" t="s">
-        <v>164</v>
-      </c>
       <c r="P24" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
@@ -2710,22 +2707,22 @@
         <v>46034</v>
       </c>
       <c r="C25" s="50" t="s">
+        <v>164</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="F25" s="5" t="s">
         <v>167</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>168</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>55</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I25" s="5" t="s">
         <v>31</v>
@@ -2740,16 +2737,16 @@
         <v>22</v>
       </c>
       <c r="M25" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="N25" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="N25" s="5" t="s">
+      <c r="O25" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="O25" s="5" t="s">
+      <c r="P25" s="52" t="s">
         <v>171</v>
-      </c>
-      <c r="P25" s="52" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="26" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
@@ -2761,22 +2758,22 @@
         <v>9743392738</v>
       </c>
       <c r="D26" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="E26" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="E26" s="47" t="s">
-        <v>174</v>
-      </c>
       <c r="F26" s="25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G26" s="25" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H26" s="25" t="s">
         <v>19</v>
       </c>
       <c r="I26" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J26" s="25">
         <v>3</v>
@@ -2788,13 +2785,13 @@
         <v>70</v>
       </c>
       <c r="M26" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="N26" s="54" t="s">
         <v>175</v>
       </c>
-      <c r="N26" s="54" t="s">
+      <c r="O26" s="48" t="s">
         <v>176</v>
-      </c>
-      <c r="O26" s="48" t="s">
-        <v>177</v>
       </c>
       <c r="P26" s="25" t="s">
         <v>26</v>
@@ -2808,22 +2805,22 @@
         <v>9744166997</v>
       </c>
       <c r="D27" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="E27" s="47" t="s">
         <v>178</v>
       </c>
-      <c r="E27" s="47" t="s">
+      <c r="F27" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="G27" s="25" t="s">
         <v>179</v>
       </c>
-      <c r="F27" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="G27" s="25" t="s">
+      <c r="H27" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="I27" s="25" t="s">
         <v>180</v>
-      </c>
-      <c r="H27" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="I27" s="25" t="s">
-        <v>181</v>
       </c>
       <c r="J27" s="25">
         <v>3</v>
@@ -2835,21 +2832,21 @@
         <v>70</v>
       </c>
       <c r="M27" s="53" t="s">
+        <v>181</v>
+      </c>
+      <c r="N27" s="25" t="s">
         <v>182</v>
       </c>
-      <c r="N27" s="25" t="s">
+      <c r="O27" s="55" t="s">
         <v>183</v>
       </c>
-      <c r="O27" s="55" t="s">
+      <c r="P27" s="25" t="s">
         <v>184</v>
-      </c>
-      <c r="P27" s="25" t="s">
-        <v>185</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B2:P27" xr:uid="{DDFA68B3-D723-4F82-915D-45274FA59027}">
-    <filterColumn colId="7">
+    <filterColumn colId="5">
       <filters>
         <filter val="SA"/>
       </filters>
@@ -2915,23 +2912,23 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="56" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="56" t="s">
         <v>186</v>
-      </c>
-      <c r="B1" s="56" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B3" t="s">
         <v>39</v>
@@ -2939,7 +2936,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B4" t="s">
         <v>32</v>
@@ -2947,15 +2944,15 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B6" t="s">
         <v>31</v>
@@ -2963,15 +2960,15 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
@@ -2979,31 +2976,31 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>194</v>
+      </c>
+      <c r="B9" t="s">
         <v>195</v>
-      </c>
-      <c r="B9" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>197</v>
+      </c>
+      <c r="B11" t="s">
         <v>198</v>
-      </c>
-      <c r="B11" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B12" t="s">
         <v>55</v>
@@ -3011,7 +3008,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B13" t="s">
         <v>38</v>
@@ -3019,7 +3016,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B14" t="s">
         <v>68</v>
@@ -3027,7 +3024,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B15" t="s">
         <v>61</v>
@@ -3035,15 +3032,15 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s">
         <v>47</v>
@@ -3051,7 +3048,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B18" t="s">
         <v>30</v>
@@ -3059,95 +3056,95 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>209</v>
+      </c>
+      <c r="B22" t="s">
         <v>210</v>
-      </c>
-      <c r="B22" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>211</v>
+      </c>
+      <c r="B23" t="s">
         <v>212</v>
-      </c>
-      <c r="B23" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>213</v>
+      </c>
+      <c r="B24" t="s">
         <v>214</v>
-      </c>
-      <c r="B24" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>215</v>
+      </c>
+      <c r="B25" t="s">
         <v>216</v>
-      </c>
-      <c r="B25" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>217</v>
+      </c>
+      <c r="B26" t="s">
         <v>218</v>
-      </c>
-      <c r="B26" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>219</v>
+      </c>
+      <c r="B27" t="s">
         <v>220</v>
-      </c>
-      <c r="B27" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>221</v>
+      </c>
+      <c r="B28" t="s">
         <v>222</v>
-      </c>
-      <c r="B28" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="57" t="s">
+        <v>223</v>
+      </c>
+      <c r="B29" s="57" t="s">
         <v>224</v>
-      </c>
-      <c r="B29" s="57" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="57" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B30" s="57" t="s">
         <v>20</v>
@@ -3155,15 +3152,15 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="57" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B31" s="57" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="57" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B32" s="57" t="s">
         <v>18</v>
@@ -3171,7 +3168,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="57" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B33" s="57" t="s">
         <v>62</v>
@@ -3179,58 +3176,58 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="57" t="s">
+        <v>229</v>
+      </c>
+      <c r="B34" s="57" t="s">
         <v>230</v>
-      </c>
-      <c r="B34" s="57" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="57" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B35" s="57" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="57" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B36" s="57" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="57" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B37" s="57" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="57" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B38" s="57" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="57" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B39" s="57" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="57" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B40" s="57" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -3249,13 +3246,13 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -3269,7 +3266,7 @@
         <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
         <v>26</v>
@@ -3286,10 +3283,10 @@
         <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -3300,7 +3297,7 @@
         <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -3320,17 +3317,17 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">

--- a/LP_Error_Log.xlsx
+++ b/LP_Error_Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://musigma-my.sharepoint.com/personal/maria_daniels_mu-sigma_com/Documents/Documents/exel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="8_{5EB6F39B-016E-4168-A8C8-22C4E1775C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD65717F-C4D8-4C8A-A452-759C7E7DB61F}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="8_{5EB6F39B-016E-4168-A8C8-22C4E1775C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{331833D1-2995-415D-8C01-C3871C4F3724}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{7E36AAAB-D706-4463-8B8E-FC781FC93857}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7E36AAAB-D706-4463-8B8E-FC781FC93857}"/>
   </bookViews>
   <sheets>
     <sheet name="Error Log" sheetId="1" r:id="rId1"/>
@@ -1620,7 +1620,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDFA68B3-D723-4F82-915D-45274FA59027}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A2:Q27"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1692,7 +1691,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="2:16" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B3" s="10">
         <v>45846</v>
       </c>
@@ -1739,7 +1738,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="2:16" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:16" ht="29" x14ac:dyDescent="0.35">
       <c r="B4" s="15">
         <v>45875</v>
       </c>
@@ -1786,7 +1785,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="2:16" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:16" ht="29" x14ac:dyDescent="0.35">
       <c r="B5" s="15">
         <v>45896</v>
       </c>
@@ -1833,7 +1832,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B6" s="10" t="s">
         <v>43</v>
       </c>
@@ -1880,7 +1879,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="B7" s="10" t="s">
         <v>51</v>
       </c>
@@ -1925,7 +1924,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="2:16" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:16" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B8" s="15">
         <v>45890</v>
       </c>
@@ -1972,7 +1971,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="2:16" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:16" ht="29" x14ac:dyDescent="0.35">
       <c r="B9" s="18">
         <v>45873</v>
       </c>
@@ -2066,7 +2065,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B11" s="22">
         <v>45876</v>
       </c>
@@ -2113,7 +2112,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B12" s="23">
         <v>45833</v>
       </c>
@@ -2158,7 +2157,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="2:16" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B13" s="7">
         <v>45896</v>
       </c>
@@ -2205,7 +2204,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B14" s="7">
         <v>45929</v>
       </c>
@@ -2246,7 +2245,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="2:16" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:16" ht="29" x14ac:dyDescent="0.35">
       <c r="B15" s="7">
         <v>45849</v>
       </c>
@@ -2293,7 +2292,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="2:16" ht="76.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:16" ht="76.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="7">
         <v>45929</v>
       </c>
@@ -2340,7 +2339,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="2:16" ht="39.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:16" ht="39.5" x14ac:dyDescent="0.35">
       <c r="B17" s="7">
         <v>45966</v>
       </c>
@@ -2387,7 +2386,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="2:16" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B18" s="7">
         <v>45938</v>
       </c>
@@ -2432,7 +2431,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="2:16" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:16" ht="87" x14ac:dyDescent="0.35">
       <c r="B19" s="36">
         <v>45942</v>
       </c>
@@ -2477,7 +2476,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B20" s="40">
         <v>45788</v>
       </c>
@@ -2524,7 +2523,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="2:16" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:16" ht="29" x14ac:dyDescent="0.35">
       <c r="B21" s="40">
         <v>45966</v>
       </c>
@@ -2568,7 +2567,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B22" s="40">
         <v>45978</v>
       </c>
@@ -2615,7 +2614,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="2:16" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:16" ht="87" x14ac:dyDescent="0.35">
       <c r="B23" s="40"/>
       <c r="C23" s="43"/>
       <c r="E23" s="1" t="s">
@@ -2655,7 +2654,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="24" spans="2:16" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="B24" s="44" t="s">
         <v>156</v>
       </c>
@@ -2702,7 +2701,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="25" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B25" s="49">
         <v>46034</v>
       </c>
@@ -2749,7 +2748,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="26" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B26" s="7">
         <v>46044</v>
       </c>
@@ -2797,7 +2796,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="2:16" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:16" ht="101.5" x14ac:dyDescent="0.35">
       <c r="B27" s="7">
         <v>46072</v>
       </c>
@@ -2845,13 +2844,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:P27" xr:uid="{DDFA68B3-D723-4F82-915D-45274FA59027}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="SA"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B2:P27" xr:uid="{DDFA68B3-D723-4F82-915D-45274FA59027}"/>
   <conditionalFormatting sqref="B19">
     <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
